--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92553669283</v>
+        <v>46157.93108005249</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108005249</v>
+        <v>46157.93132662508</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93132662508</v>
+        <v>46157.93380678765</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93380678765</v>
+        <v>46157.93691446681</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93691446681</v>
+        <v>46158.28203408485</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203408485</v>
+        <v>46158.2973509778</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2973509778</v>
+        <v>46158.29803977594</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29803977594</v>
+        <v>46158.33367523894</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33367523894</v>
+        <v>46158.37219294073</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37219294073</v>
+        <v>46158.37273981306</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
